--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487030_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487030_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.3364</v>
+        <v>4.7269</v>
       </c>
       <c r="E2" t="n">
-        <v>3.7898</v>
+        <v>4.4175</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5466</v>
+        <v>0.3095</v>
       </c>
       <c r="G2" t="n">
         <v>2.2482</v>
@@ -610,13 +610,13 @@
         <v>2.0534</v>
       </c>
       <c r="S2" t="n">
-        <v>1.2134</v>
+        <v>1.6039</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0618</v>
+        <v>0.6894</v>
       </c>
       <c r="U2" t="n">
-        <v>1.1516</v>
+        <v>0.9145</v>
       </c>
       <c r="V2" t="n">
         <v>-1.1786</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5964</v>
+        <v>3.1087</v>
       </c>
       <c r="E3" t="n">
-        <v>2.6199</v>
+        <v>2.895</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0235</v>
+        <v>0.2137</v>
       </c>
       <c r="G3" t="n">
         <v>-0.3712</v>
@@ -688,13 +688,13 @@
         <v>2.4641</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5570000000000001</v>
+        <v>1.0692</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5615</v>
+        <v>0.8366</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0046</v>
+        <v>0.2326</v>
       </c>
       <c r="V3" t="n">
         <v>1.1786</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.578</v>
+        <v>1.307</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7423</v>
+        <v>0.5603</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8357</v>
+        <v>0.7468</v>
       </c>
       <c r="G4" t="n">
         <v>0.2426</v>
@@ -766,13 +766,13 @@
         <v>1.6427</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9247</v>
+        <v>0.6536999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6274</v>
+        <v>0.4454</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2973</v>
+        <v>0.2084</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. SMITH</t>
+          <t>H. FIGUEROA ÁLVAREZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.089</v>
+        <v>0.8411999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>2.5072</v>
+        <v>1.2368</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.4182</v>
+        <v>-0.3956</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.6879999999999999</v>
+        <v>-3.8874</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.8302</v>
+        <v>0.7887</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1422</v>
+        <v>-4.6761</v>
       </c>
       <c r="J5" t="n">
-        <v>1.6241</v>
+        <v>-1.3492</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.1649</v>
+        <v>1.7038</v>
       </c>
       <c r="L5" t="n">
-        <v>1.789</v>
+        <v>-3.053</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.3121</v>
+        <v>-2.5382</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6653</v>
+        <v>-0.9151</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.6468</v>
+        <v>-1.6231</v>
       </c>
       <c r="P5" t="n">
-        <v>1.0267</v>
+        <v>0.8214</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.2321</v>
       </c>
       <c r="R5" t="n">
-        <v>1.0267</v>
+        <v>2.0534</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2308</v>
+        <v>1.4412</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8832</v>
+        <v>0.8715000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6524</v>
+        <v>0.5697</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.4805</v>
+        <v>2.4661</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.9466</v>
       </c>
       <c r="X5" t="n">
         <v>-0.4805</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>H. FIGUEROA ÁLVAREZ</t>
+          <t>A. SMITH</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2846</v>
+        <v>-0.0857</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2295</v>
+        <v>2.1547</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5141</v>
+        <v>-2.2404</v>
       </c>
       <c r="G6" t="n">
-        <v>-3.8874</v>
+        <v>-0.6879999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7887</v>
+        <v>-0.8302</v>
       </c>
       <c r="I6" t="n">
-        <v>-4.6761</v>
+        <v>0.1422</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.3492</v>
+        <v>1.6241</v>
       </c>
       <c r="K6" t="n">
-        <v>1.7038</v>
+        <v>-0.1649</v>
       </c>
       <c r="L6" t="n">
-        <v>-3.053</v>
+        <v>1.789</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.5382</v>
+        <v>-2.3121</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.9151</v>
+        <v>-0.6653</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.6231</v>
+        <v>-1.6468</v>
       </c>
       <c r="P6" t="n">
-        <v>0.8214</v>
+        <v>1.0267</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.2321</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.0534</v>
+        <v>1.0267</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3153</v>
+        <v>0.0561</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1358</v>
+        <v>0.5306</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4511</v>
+        <v>-0.4745</v>
       </c>
       <c r="V6" t="n">
-        <v>2.4661</v>
+        <v>-0.4805</v>
       </c>
       <c r="W6" t="n">
-        <v>2.9466</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>-0.4805</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.641</v>
+        <v>-0.7917</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2683</v>
+        <v>0.2955</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9093</v>
+        <v>-1.0871</v>
       </c>
       <c r="G7" t="n">
         <v>-0.9598</v>
@@ -1000,13 +1000,13 @@
         <v>1.8481</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2921</v>
+        <v>0.1414</v>
       </c>
       <c r="T7" t="n">
-        <v>0.06950000000000001</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2226</v>
+        <v>0.0447</v>
       </c>
       <c r="V7" t="n">
         <v>-0.5893</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>O. BIESHAAR</t>
+          <t>G. VAZQUEZ VALLEJO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8536</v>
+        <v>-1.0354</v>
       </c>
       <c r="E8" t="n">
-        <v>2.7499</v>
+        <v>0.2057</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.6035</v>
+        <v>-1.2411</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.5102</v>
+        <v>-5.7925</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.4499</v>
+        <v>-0.0907</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.0603</v>
+        <v>-5.7018</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.3037</v>
+        <v>-2.6597</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.1455</v>
+        <v>0.6297</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.1582</v>
+        <v>-3.2894</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.2064</v>
+        <v>-3.1328</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.3044</v>
+        <v>-0.7204</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.902</v>
+        <v>-2.4124</v>
       </c>
       <c r="P8" t="n">
-        <v>1.2321</v>
+        <v>-0.2053</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.2053</v>
+        <v>-2.0534</v>
       </c>
       <c r="R8" t="n">
-        <v>1.4374</v>
+        <v>1.8481</v>
       </c>
       <c r="S8" t="n">
-        <v>1.4245</v>
+        <v>1.4266</v>
       </c>
       <c r="T8" t="n">
-        <v>2.0803</v>
+        <v>1.3829</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6558</v>
+        <v>0.0437</v>
       </c>
       <c r="V8" t="n">
+        <v>3.5359</v>
+      </c>
+      <c r="W8" t="n">
+        <v>3.5359</v>
+      </c>
+      <c r="X8" t="n">
         <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.1786</v>
-      </c>
-      <c r="X8" t="n">
-        <v>-1.1786</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. VAZQUEZ VALLEJO</t>
+          <t>O. BIESHAAR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0057</v>
+        <v>-2.1706</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2057</v>
+        <v>1.5218</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2114</v>
+        <v>-3.6924</v>
       </c>
       <c r="G9" t="n">
-        <v>-5.7925</v>
+        <v>-3.5102</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.0907</v>
+        <v>-1.4499</v>
       </c>
       <c r="I9" t="n">
-        <v>-5.7018</v>
+        <v>-2.0603</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.6597</v>
+        <v>-0.3037</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6297</v>
+        <v>-0.1455</v>
       </c>
       <c r="L9" t="n">
-        <v>-3.2894</v>
+        <v>-0.1582</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.1328</v>
+        <v>-3.2064</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7204</v>
+        <v>-1.3044</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.4124</v>
+        <v>-1.902</v>
       </c>
       <c r="P9" t="n">
+        <v>1.2321</v>
+      </c>
+      <c r="Q9" t="n">
         <v>-0.2053</v>
       </c>
-      <c r="Q9" t="n">
-        <v>-2.0534</v>
-      </c>
       <c r="R9" t="n">
-        <v>1.8481</v>
+        <v>1.4374</v>
       </c>
       <c r="S9" t="n">
-        <v>1.4563</v>
+        <v>0.1075</v>
       </c>
       <c r="T9" t="n">
-        <v>1.3829</v>
+        <v>0.8522</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0733</v>
+        <v>-0.7447</v>
       </c>
       <c r="V9" t="n">
-        <v>3.5359</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>3.5359</v>
+        <v>1.1786</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.2303</v>
+        <v>-2.2896</v>
       </c>
       <c r="E10" t="n">
         <v>-0.2362</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.9942</v>
+        <v>-2.0534</v>
       </c>
       <c r="G10" t="n">
         <v>-4.1395</v>
@@ -1234,13 +1234,13 @@
         <v>1.6427</v>
       </c>
       <c r="S10" t="n">
-        <v>0.7469</v>
+        <v>0.6876</v>
       </c>
       <c r="T10" t="n">
         <v>0.8096</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.06270000000000001</v>
+        <v>-0.122</v>
       </c>
       <c r="V10" t="n">
         <v>-0.4805</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.3649</v>
+        <v>-4.7324</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.4893</v>
+        <v>-2.005</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.8756</v>
+        <v>-2.7274</v>
       </c>
       <c r="G11" t="n">
         <v>-4.2346</v>
@@ -1312,13 +1312,13 @@
         <v>1.4374</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.389</v>
+        <v>-0.7565</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5115</v>
+        <v>-0.0272</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.8774999999999999</v>
+        <v>-0.7292999999999999</v>
       </c>
       <c r="V11" t="n">
         <v>-1.1786</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.7803</v>
+        <v>-1.121600000000002</v>
       </c>
       <c r="E12" t="n">
-        <v>10.3871</v>
+        <v>11.0461</v>
       </c>
       <c r="F12" t="n">
-        <v>-12.1675</v>
+        <v>-12.1674</v>
       </c>
       <c r="G12" t="n">
         <v>-21.0924</v>
@@ -1375,7 +1375,7 @@
         <v>-23.9754</v>
       </c>
       <c r="N12" t="n">
-        <v>-7.6259</v>
+        <v>-7.625900000000001</v>
       </c>
       <c r="O12" t="n">
         <v>-16.3495</v>
@@ -1390,13 +1390,13 @@
         <v>17.454</v>
       </c>
       <c r="S12" t="n">
-        <v>5.771999999999999</v>
+        <v>6.4307</v>
       </c>
       <c r="T12" t="n">
-        <v>5.828899999999999</v>
+        <v>6.4877</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.05709999999999993</v>
+        <v>-0.05689999999999995</v>
       </c>
       <c r="V12" t="n">
         <v>3.273099999999999</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. BOIX COLET</t>
+          <t>J. JUANOLA MADERA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.7992</v>
+        <v>4.734</v>
       </c>
       <c r="E13" t="n">
-        <v>4.9928</v>
+        <v>6.4423</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.1936</v>
+        <v>-1.7083</v>
       </c>
       <c r="G13" t="n">
-        <v>6.4833</v>
+        <v>3.9757</v>
       </c>
       <c r="H13" t="n">
-        <v>0.7654</v>
+        <v>0.5448</v>
       </c>
       <c r="I13" t="n">
-        <v>5.7179</v>
+        <v>3.4308</v>
       </c>
       <c r="J13" t="n">
-        <v>7.0077</v>
+        <v>5.7162</v>
       </c>
       <c r="K13" t="n">
-        <v>1.7588</v>
+        <v>2.1252</v>
       </c>
       <c r="L13" t="n">
-        <v>5.2489</v>
+        <v>3.591</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.5244</v>
+        <v>-1.7405</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.9933999999999999</v>
+        <v>-1.5804</v>
       </c>
       <c r="O13" t="n">
-        <v>0.469</v>
+        <v>-0.1602</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.4374</v>
+        <v>-0.8214</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.6694</v>
+        <v>-2.2588</v>
       </c>
       <c r="R13" t="n">
-        <v>1.2321</v>
+        <v>1.4374</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.4869</v>
+        <v>-0.0794</v>
       </c>
       <c r="T13" t="n">
-        <v>0.4144</v>
+        <v>0.1471</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.9013</v>
+        <v>-0.2265</v>
       </c>
       <c r="V13" t="n">
-        <v>0.2402</v>
+        <v>1.6591</v>
       </c>
       <c r="W13" t="n">
-        <v>0.2402</v>
+        <v>2.8377</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. JUANOLA MADERA</t>
+          <t>J. BOIX COLET</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.287</v>
+        <v>4.1898</v>
       </c>
       <c r="E14" t="n">
-        <v>5.7101</v>
+        <v>4.4698</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.4231</v>
+        <v>-0.28</v>
       </c>
       <c r="G14" t="n">
-        <v>3.9757</v>
+        <v>6.4833</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5448</v>
+        <v>0.7654</v>
       </c>
       <c r="I14" t="n">
-        <v>3.4308</v>
+        <v>5.7179</v>
       </c>
       <c r="J14" t="n">
-        <v>5.7162</v>
+        <v>7.0077</v>
       </c>
       <c r="K14" t="n">
-        <v>2.1252</v>
+        <v>1.7588</v>
       </c>
       <c r="L14" t="n">
-        <v>3.591</v>
+        <v>5.2489</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.7405</v>
+        <v>-0.5244</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.5804</v>
+        <v>-0.9933999999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.1602</v>
+        <v>0.469</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.8214</v>
+        <v>-1.4374</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.2588</v>
+        <v>-2.6694</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4374</v>
+        <v>1.2321</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.5264</v>
+        <v>-1.0963</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5851</v>
+        <v>-0.1087</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.9413</v>
+        <v>-0.9877</v>
       </c>
       <c r="V14" t="n">
-        <v>1.6591</v>
+        <v>0.2402</v>
       </c>
       <c r="W14" t="n">
-        <v>2.8377</v>
+        <v>0.2402</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.1786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.0948</v>
+        <v>2.5201</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6143</v>
+        <v>1.7189</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4805</v>
+        <v>0.8012</v>
       </c>
       <c r="G15" t="n">
         <v>2.8648</v>
@@ -1624,13 +1624,13 @@
         <v>0.4107</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2567</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.159</v>
+        <v>-0.0544</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4156</v>
+        <v>0.7364000000000001</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.9136</v>
+        <v>1.5474</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3579</v>
+        <v>-0.2697</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5556</v>
+        <v>1.8171</v>
       </c>
       <c r="G16" t="n">
         <v>4.3438</v>
@@ -1702,13 +1702,13 @@
         <v>0.4107</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4302</v>
+        <v>0.064</v>
       </c>
       <c r="T16" t="n">
-        <v>0.612</v>
+        <v>-0.0156</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1818</v>
+        <v>0.07969999999999999</v>
       </c>
       <c r="V16" t="n">
         <v>-0.8070000000000001</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>E. KALU</t>
+          <t>F. GARRIDO TEBAN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3196</v>
+        <v>0.6543</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7584</v>
+        <v>1.6987</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.4388</v>
+        <v>-1.0445</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.3359</v>
+        <v>4.0137</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2822</v>
+        <v>-0.049</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.6181</v>
+        <v>4.0627</v>
       </c>
       <c r="J17" t="n">
-        <v>1.2735</v>
+        <v>3.4652</v>
       </c>
       <c r="K17" t="n">
-        <v>0.9183</v>
+        <v>0.3343</v>
       </c>
       <c r="L17" t="n">
-        <v>0.3552</v>
+        <v>3.1308</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.6094</v>
+        <v>0.5485</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6362</v>
+        <v>-0.3833</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.9732</v>
+        <v>0.9318</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.2321</v>
+        <v>-1.6427</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.2588</v>
+        <v>-1.6427</v>
       </c>
       <c r="R17" t="n">
-        <v>1.0267</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>1.4297</v>
+        <v>-1.1274</v>
       </c>
       <c r="T17" t="n">
-        <v>1.5651</v>
+        <v>-0.713</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1354</v>
+        <v>-0.4144</v>
       </c>
       <c r="V17" t="n">
-        <v>0.4579</v>
+        <v>-0.5893</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1786</v>
+        <v>0.5893</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.7207</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>F. GARRIDO TEBAN</t>
+          <t>J. CASTILLO CARRASCO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.07099999999999999</v>
+        <v>-0.2768</v>
       </c>
       <c r="E18" t="n">
-        <v>1.4895</v>
+        <v>1.4359</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.5605</v>
+        <v>-1.7127</v>
       </c>
       <c r="G18" t="n">
-        <v>4.0137</v>
+        <v>2.2156</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.049</v>
+        <v>-0.1367</v>
       </c>
       <c r="I18" t="n">
-        <v>4.0627</v>
+        <v>2.3522</v>
       </c>
       <c r="J18" t="n">
-        <v>3.4652</v>
+        <v>1.9513</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3343</v>
+        <v>0.1363</v>
       </c>
       <c r="L18" t="n">
-        <v>3.1308</v>
+        <v>1.8151</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5485</v>
+        <v>0.2642</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3833</v>
+        <v>-0.2729</v>
       </c>
       <c r="O18" t="n">
-        <v>0.9318</v>
+        <v>0.5372</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.6427</v>
+        <v>0.2053</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.6427</v>
+        <v>-0.4107</v>
       </c>
       <c r="R18" t="n">
+        <v>0.616</v>
+      </c>
+      <c r="S18" t="n">
+        <v>-0.9297</v>
+      </c>
+      <c r="T18" t="n">
+        <v>-0.1047</v>
+      </c>
+      <c r="U18" t="n">
+        <v>-0.825</v>
+      </c>
+      <c r="V18" t="n">
+        <v>-1.7679</v>
+      </c>
+      <c r="W18" t="n">
         <v>0</v>
       </c>
-      <c r="S18" t="n">
-        <v>-1.8526</v>
-      </c>
-      <c r="T18" t="n">
-        <v>-0.9222</v>
-      </c>
-      <c r="U18" t="n">
-        <v>-0.9304</v>
-      </c>
-      <c r="V18" t="n">
-        <v>-0.5893</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0.5893</v>
-      </c>
       <c r="X18" t="n">
-        <v>-1.1786</v>
+        <v>-1.7679</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. CASTILLO CARRASCO</t>
+          <t>E. KALU</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3465</v>
+        <v>-0.7439</v>
       </c>
       <c r="E19" t="n">
-        <v>1.6451</v>
+        <v>0.7124</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.9917</v>
+        <v>-1.4563</v>
       </c>
       <c r="G19" t="n">
-        <v>2.2156</v>
+        <v>-0.3359</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1367</v>
+        <v>0.2822</v>
       </c>
       <c r="I19" t="n">
-        <v>2.3522</v>
+        <v>-0.6181</v>
       </c>
       <c r="J19" t="n">
-        <v>1.9513</v>
+        <v>1.2735</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1363</v>
+        <v>0.9183</v>
       </c>
       <c r="L19" t="n">
-        <v>1.8151</v>
+        <v>0.3552</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2642</v>
+        <v>-1.6094</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2729</v>
+        <v>-0.6362</v>
       </c>
       <c r="O19" t="n">
-        <v>0.5372</v>
+        <v>-0.9732</v>
       </c>
       <c r="P19" t="n">
-        <v>0.2053</v>
+        <v>-1.2321</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.4107</v>
+        <v>-2.2588</v>
       </c>
       <c r="R19" t="n">
-        <v>0.616</v>
+        <v>1.0267</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9995000000000001</v>
+        <v>0.3662</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1045</v>
+        <v>0.5191</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.104</v>
+        <v>-0.1529</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.7679</v>
+        <v>0.4579</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.7679</v>
+        <v>-0.7207</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.5684</v>
+        <v>-2.0995</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.0421</v>
+        <v>-2.6237</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4737</v>
+        <v>0.5242</v>
       </c>
       <c r="G20" t="n">
         <v>-1.0176</v>
@@ -2014,13 +2014,13 @@
         <v>0.2053</v>
       </c>
       <c r="S20" t="n">
-        <v>0.057</v>
+        <v>0.526</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2635</v>
+        <v>0.1549</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3205</v>
+        <v>0.371</v>
       </c>
       <c r="V20" t="n">
         <v>0.2402</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.298</v>
+        <v>-2.5693</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.284</v>
+        <v>-2.6564</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.014</v>
+        <v>0.0871</v>
       </c>
       <c r="G21" t="n">
         <v>-1.4078</v>
@@ -2092,13 +2092,13 @@
         <v>0.8214</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1572</v>
+        <v>0.5715</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3216</v>
+        <v>0.306</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1644</v>
+        <v>0.2655</v>
       </c>
       <c r="V21" t="n">
         <v>-1.5277</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.3499</v>
+        <v>-2.6891</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9254</v>
+        <v>1.2392</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.2753</v>
+        <v>-3.9283</v>
       </c>
       <c r="G22" t="n">
         <v>-0.0431</v>
@@ -2170,13 +2170,13 @@
         <v>1.0267</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.9228</v>
+        <v>-1.262</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3875</v>
+        <v>-0.0737</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.5353</v>
+        <v>-1.1883</v>
       </c>
       <c r="V22" t="n">
         <v>-1.1786</v>
@@ -2203,19 +2203,19 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>1.7804</v>
+        <v>5.266999999999999</v>
       </c>
       <c r="E23" t="n">
         <v>12.1674</v>
       </c>
       <c r="F23" t="n">
-        <v>-10.3872</v>
+        <v>-6.900500000000001</v>
       </c>
       <c r="G23" t="n">
         <v>21.0925</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.3913999999999997</v>
+        <v>-0.3914</v>
       </c>
       <c r="I23" t="n">
         <v>21.4838</v>
@@ -2248,13 +2248,13 @@
         <v>7.187</v>
       </c>
       <c r="S23" t="n">
-        <v>-5.771800000000001</v>
+        <v>-2.2851</v>
       </c>
       <c r="T23" t="n">
-        <v>0.05709999999999987</v>
+        <v>0.05700000000000006</v>
       </c>
       <c r="U23" t="n">
-        <v>-5.829000000000001</v>
+        <v>-2.3422</v>
       </c>
       <c r="V23" t="n">
         <v>-3.2731</v>
